--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/114.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/114.xlsx
@@ -426,13 +426,13 @@
         <v>-13.46255010039493</v>
       </c>
       <c r="E2">
-        <v>-25.12801979855159</v>
+        <v>-26.08620867078258</v>
       </c>
       <c r="F2">
-        <v>-1.42781976291989</v>
+        <v>-1.339647508198508</v>
       </c>
       <c r="G2">
-        <v>-16.27370776010612</v>
+        <v>-15.48603083743206</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.79951053168856</v>
       </c>
       <c r="E3">
-        <v>-25.10292299560109</v>
+        <v>-25.0304900538484</v>
       </c>
       <c r="F3">
-        <v>-1.337556708873841</v>
+        <v>-0.6497856202492875</v>
       </c>
       <c r="G3">
-        <v>-16.40023494465987</v>
+        <v>-15.75976674602873</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.09673377733852</v>
       </c>
       <c r="E4">
-        <v>-26.20197910878867</v>
+        <v>-24.02298609967388</v>
       </c>
       <c r="F4">
-        <v>-1.265994877313395</v>
+        <v>-0.6804037361915629</v>
       </c>
       <c r="G4">
-        <v>-16.56207463563636</v>
+        <v>-14.43233379865836</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.30367944820268</v>
       </c>
       <c r="E5">
-        <v>-26.27245122129604</v>
+        <v>-24.46807622446578</v>
       </c>
       <c r="F5">
-        <v>-1.165938035464048</v>
+        <v>-1.237117989651804</v>
       </c>
       <c r="G5">
-        <v>-16.30506475393895</v>
+        <v>-15.72001474683606</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.43212621475522</v>
       </c>
       <c r="E6">
-        <v>-25.79931172850063</v>
+        <v>-26.4380892150746</v>
       </c>
       <c r="F6">
-        <v>-1.174561340127191</v>
+        <v>-0.7334233918077452</v>
       </c>
       <c r="G6">
-        <v>-16.03045275918591</v>
+        <v>-14.4879865975281</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.48345863108995</v>
       </c>
       <c r="E7">
-        <v>-26.93389372027839</v>
+        <v>-27.51177228839721</v>
       </c>
       <c r="F7">
-        <v>-0.91783122954936</v>
+        <v>-0.3718849239581094</v>
       </c>
       <c r="G7">
-        <v>-15.79815703827424</v>
+        <v>-14.73738240459681</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.45576165581401</v>
       </c>
       <c r="E8">
-        <v>-28.03487896339325</v>
+        <v>-27.80416226965046</v>
       </c>
       <c r="F8">
-        <v>-0.5118375966610859</v>
+        <v>-0.1955934300291242</v>
       </c>
       <c r="G8">
-        <v>-15.46142987879012</v>
+        <v>-15.65257744073558</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.3519861209969</v>
       </c>
       <c r="E9">
-        <v>-27.16717353030953</v>
+        <v>-28.35742858153759</v>
       </c>
       <c r="F9">
-        <v>-0.4571487807282625</v>
+        <v>-0.7365463369162993</v>
       </c>
       <c r="G9">
-        <v>-15.58185071002174</v>
+        <v>-15.36465353011586</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.17009307063224</v>
       </c>
       <c r="E10">
-        <v>-28.34574059012379</v>
+        <v>-28.04334268131359</v>
       </c>
       <c r="F10">
-        <v>-0.2883912883277389</v>
+        <v>0.2854328938373263</v>
       </c>
       <c r="G10">
-        <v>-15.08725085642651</v>
+        <v>-16.32394982462434</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.90741409760323</v>
       </c>
       <c r="E11">
-        <v>-29.17042552013465</v>
+        <v>-28.97162551119792</v>
       </c>
       <c r="F11">
-        <v>-0.3852183256735702</v>
+        <v>0.6255141608522465</v>
       </c>
       <c r="G11">
-        <v>-14.97939710376756</v>
+        <v>-14.83918230347859</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.57123398980974</v>
       </c>
       <c r="E12">
-        <v>-30.33120926252079</v>
+        <v>-28.76023634451986</v>
       </c>
       <c r="F12">
-        <v>-0.1561565147166454</v>
+        <v>0.5553100234649885</v>
       </c>
       <c r="G12">
-        <v>-13.16496197132284</v>
+        <v>-13.69938765159583</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.15634810222683</v>
       </c>
       <c r="E13">
-        <v>-31.57893291314319</v>
+        <v>-32.22420649568116</v>
       </c>
       <c r="F13">
-        <v>0.1035449497350276</v>
+        <v>0.1794399711795183</v>
       </c>
       <c r="G13">
-        <v>-14.33298661289227</v>
+        <v>-14.75002331065457</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.67738928678431</v>
       </c>
       <c r="E14">
-        <v>-32.16782699428566</v>
+        <v>-32.09863417568546</v>
       </c>
       <c r="F14">
-        <v>0.1806112826870769</v>
+        <v>0.637510577579589</v>
       </c>
       <c r="G14">
-        <v>-13.110821815592</v>
+        <v>-13.4419430080418</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.13923526281671</v>
       </c>
       <c r="E15">
-        <v>-32.41950146573596</v>
+        <v>-33.55574540747453</v>
       </c>
       <c r="F15">
-        <v>0.3618671824610395</v>
+        <v>0.457772246887555</v>
       </c>
       <c r="G15">
-        <v>-13.58960782188149</v>
+        <v>-14.16936685921978</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.54926585363099</v>
       </c>
       <c r="E16">
-        <v>-33.7958383066502</v>
+        <v>-32.46724969567283</v>
       </c>
       <c r="F16">
-        <v>0.4855937944779792</v>
+        <v>1.109259186534685</v>
       </c>
       <c r="G16">
-        <v>-12.87317606292766</v>
+        <v>-13.45167839240868</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.92338406457696</v>
       </c>
       <c r="E17">
-        <v>-33.38491325400917</v>
+        <v>-33.14315614063568</v>
       </c>
       <c r="F17">
-        <v>0.2167521241038165</v>
+        <v>0.8538238142074295</v>
       </c>
       <c r="G17">
-        <v>-12.3117721789929</v>
+        <v>-12.59255943272082</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.26762674038969</v>
       </c>
       <c r="E18">
-        <v>-34.80836660273623</v>
+        <v>-35.20364577768076</v>
       </c>
       <c r="F18">
-        <v>0.697699753067001</v>
+        <v>1.316546531941622</v>
       </c>
       <c r="G18">
-        <v>-11.20687331839485</v>
+        <v>-12.0613395059114</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.604999215337813</v>
       </c>
       <c r="E19">
-        <v>-34.76374754833865</v>
+        <v>-35.40718483466651</v>
       </c>
       <c r="F19">
-        <v>0.4530538661612091</v>
+        <v>0.7434272904363394</v>
       </c>
       <c r="G19">
-        <v>-10.92143329249563</v>
+        <v>-12.00240548548222</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.950543656453775</v>
       </c>
       <c r="E20">
-        <v>-36.32644920856456</v>
+        <v>-34.72852281326999</v>
       </c>
       <c r="F20">
-        <v>0.8925483335535007</v>
+        <v>1.758748932373665</v>
       </c>
       <c r="G20">
-        <v>-11.60108255776809</v>
+        <v>-10.27346094015805</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.312893324101376</v>
       </c>
       <c r="E21">
-        <v>-36.34208150083904</v>
+        <v>-37.40657177192608</v>
       </c>
       <c r="F21">
-        <v>0.906198171616831</v>
+        <v>1.787143710206827</v>
       </c>
       <c r="G21">
-        <v>-11.51788718512837</v>
+        <v>-12.35890692669433</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.706946042997494</v>
       </c>
       <c r="E22">
-        <v>-37.97856332383493</v>
+        <v>-36.59594322523503</v>
       </c>
       <c r="F22">
-        <v>0.4303325766698214</v>
+        <v>0.7027345701412164</v>
       </c>
       <c r="G22">
-        <v>-11.23594494141153</v>
+        <v>-11.25090074927948</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.12811113043661</v>
       </c>
       <c r="E23">
-        <v>-36.84173747318636</v>
+        <v>-39.07095352328322</v>
       </c>
       <c r="F23">
-        <v>0.9655473825578044</v>
+        <v>1.625675022583536</v>
       </c>
       <c r="G23">
-        <v>-11.4514522922143</v>
+        <v>-11.50179935582242</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.579081890186807</v>
       </c>
       <c r="E24">
-        <v>-38.23829395054486</v>
+        <v>-37.823929521895</v>
       </c>
       <c r="F24">
-        <v>0.9831319657844323</v>
+        <v>1.237046455560148</v>
       </c>
       <c r="G24">
-        <v>-10.87751414192246</v>
+        <v>-10.63068425011324</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.057788525725072</v>
       </c>
       <c r="E25">
-        <v>-37.68413100080421</v>
+        <v>-37.97000224372342</v>
       </c>
       <c r="F25">
-        <v>0.9280571306419043</v>
+        <v>2.204410595079799</v>
       </c>
       <c r="G25">
-        <v>-10.57153366906113</v>
+        <v>-10.4199313893501</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.553415496978374</v>
       </c>
       <c r="E26">
-        <v>-37.80953576726163</v>
+        <v>-39.70781320111494</v>
       </c>
       <c r="F26">
-        <v>0.5285463010479392</v>
+        <v>2.347675080659168</v>
       </c>
       <c r="G26">
-        <v>-10.89518023879851</v>
+        <v>-10.05841624159516</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.072718114724598</v>
       </c>
       <c r="E27">
-        <v>-38.28969439476892</v>
+        <v>-38.75362523566973</v>
       </c>
       <c r="F27">
-        <v>0.6788568797555207</v>
+        <v>1.806466208244528</v>
       </c>
       <c r="G27">
-        <v>-10.35733880688213</v>
+        <v>-9.492845206279913</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.611130795959673</v>
       </c>
       <c r="E28">
-        <v>-37.48040401214714</v>
+        <v>-39.59803166998399</v>
       </c>
       <c r="F28">
-        <v>0.7286011706610338</v>
+        <v>1.773508782756747</v>
       </c>
       <c r="G28">
-        <v>-11.08586186728252</v>
+        <v>-9.878756236329325</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.172307750560951</v>
       </c>
       <c r="E29">
-        <v>-37.60531970341172</v>
+        <v>-38.94431927613273</v>
       </c>
       <c r="F29">
-        <v>0.9040510433087747</v>
+        <v>1.591826273770343</v>
       </c>
       <c r="G29">
-        <v>-11.18807191885923</v>
+        <v>-8.82099212343269</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.763722608224221</v>
       </c>
       <c r="E30">
-        <v>-36.77044797112061</v>
+        <v>-38.46882271261633</v>
       </c>
       <c r="F30">
-        <v>0.6088971107520884</v>
+        <v>1.558484485807663</v>
       </c>
       <c r="G30">
-        <v>-10.6202335594464</v>
+        <v>-9.501917783891777</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.386626288120663</v>
       </c>
       <c r="E31">
-        <v>-37.33567171862499</v>
+        <v>-39.04555784104821</v>
       </c>
       <c r="F31">
-        <v>0.4882603091475908</v>
+        <v>1.601572844631682</v>
       </c>
       <c r="G31">
-        <v>-10.27672247438814</v>
+        <v>-10.23523470899052</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.054719676292336</v>
       </c>
       <c r="E32">
-        <v>-36.57234534718106</v>
+        <v>-37.82283136694814</v>
       </c>
       <c r="F32">
-        <v>0.5070451967408752</v>
+        <v>1.459232817073837</v>
       </c>
       <c r="G32">
-        <v>-10.46698082529098</v>
+        <v>-9.70292869784492</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.777749483447022</v>
       </c>
       <c r="E33">
-        <v>-35.64198394772721</v>
+        <v>-37.30082058266196</v>
       </c>
       <c r="F33">
-        <v>0.5212939444364295</v>
+        <v>1.362737955056528</v>
       </c>
       <c r="G33">
-        <v>-10.90043347451519</v>
+        <v>-9.838617052992637</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.564249609543882</v>
       </c>
       <c r="E34">
-        <v>-36.76786447669924</v>
+        <v>-37.15544524583072</v>
       </c>
       <c r="F34">
-        <v>0.3983642218609829</v>
+        <v>1.086619905416174</v>
       </c>
       <c r="G34">
-        <v>-10.76106686999933</v>
+        <v>-10.17989362616892</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.425243621545295</v>
       </c>
       <c r="E35">
-        <v>-35.16778026354</v>
+        <v>-33.95155667811495</v>
       </c>
       <c r="F35">
-        <v>0.3897400888304373</v>
+        <v>1.480927759353156</v>
       </c>
       <c r="G35">
-        <v>-10.8729565251764</v>
+        <v>-11.43231948930117</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.363722492778931</v>
       </c>
       <c r="E36">
-        <v>-35.34994492320956</v>
+        <v>-36.37933046378914</v>
       </c>
       <c r="F36">
-        <v>0.7213065673119814</v>
+        <v>1.617676306942104</v>
       </c>
       <c r="G36">
-        <v>-11.12615526803251</v>
+        <v>-10.74271499781736</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.37973376046087</v>
       </c>
       <c r="E37">
-        <v>-34.00410961897397</v>
+        <v>-36.80939058334958</v>
       </c>
       <c r="F37">
-        <v>0.8630336029917544</v>
+        <v>1.508558782440936</v>
       </c>
       <c r="G37">
-        <v>-11.33529704900995</v>
+        <v>-9.423854241771028</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.47210333970165</v>
       </c>
       <c r="E38">
-        <v>-33.9337552467908</v>
+        <v>-32.36250609187541</v>
       </c>
       <c r="F38">
-        <v>1.163119635064709</v>
+        <v>1.214768342629258</v>
       </c>
       <c r="G38">
-        <v>-11.49863625823911</v>
+        <v>-10.16219471707728</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.63095491166544</v>
       </c>
       <c r="E39">
-        <v>-33.45581104307326</v>
+        <v>-33.75404954850742</v>
       </c>
       <c r="F39">
-        <v>1.024664650625994</v>
+        <v>1.894071031294993</v>
       </c>
       <c r="G39">
-        <v>-11.56690535400492</v>
+        <v>-12.02121672868251</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.846846162193118</v>
       </c>
       <c r="E40">
-        <v>-32.9581974125034</v>
+        <v>-34.03476512376889</v>
       </c>
       <c r="F40">
-        <v>1.191935223538493</v>
+        <v>1.81150599552316</v>
       </c>
       <c r="G40">
-        <v>-12.20001049145666</v>
+        <v>-10.94993398296097</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.108307940371947</v>
       </c>
       <c r="E41">
-        <v>-32.95956954012772</v>
+        <v>-33.51461554229986</v>
       </c>
       <c r="F41">
-        <v>1.268709971164756</v>
+        <v>1.810525208518246</v>
       </c>
       <c r="G41">
-        <v>-11.94214257032146</v>
+        <v>-12.50456035171808</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.399351809645947</v>
       </c>
       <c r="E42">
-        <v>-32.87160393252873</v>
+        <v>-31.73782574488732</v>
       </c>
       <c r="F42">
-        <v>1.127812959622588</v>
+        <v>2.072257829841583</v>
       </c>
       <c r="G42">
-        <v>-12.76328795290185</v>
+        <v>-11.45233494081379</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.708066906386428</v>
       </c>
       <c r="E43">
-        <v>-30.87264946453688</v>
+        <v>-33.83348124683896</v>
       </c>
       <c r="F43">
-        <v>1.424751195564905</v>
+        <v>1.883360240776795</v>
       </c>
       <c r="G43">
-        <v>-12.66712847388077</v>
+        <v>-12.7177249103274</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.020591884034673</v>
       </c>
       <c r="E44">
-        <v>-30.74765226074016</v>
+        <v>-30.50047456397949</v>
       </c>
       <c r="F44">
-        <v>1.436210830215233</v>
+        <v>2.081369871272378</v>
       </c>
       <c r="G44">
-        <v>-12.81679155165016</v>
+        <v>-11.81658006490619</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.323519123491182</v>
       </c>
       <c r="E45">
-        <v>-31.09105776592683</v>
+        <v>-32.9806880786625</v>
       </c>
       <c r="F45">
-        <v>1.617788964908885</v>
+        <v>1.870616636652128</v>
       </c>
       <c r="G45">
-        <v>-13.14186873398747</v>
+        <v>-12.08155183071758</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.612002242076981</v>
       </c>
       <c r="E46">
-        <v>-29.54927312714234</v>
+        <v>-29.81475038736801</v>
       </c>
       <c r="F46">
-        <v>1.519117153357019</v>
+        <v>2.483603544519345</v>
       </c>
       <c r="G46">
-        <v>-13.12546918863336</v>
+        <v>-12.39497083285418</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.879164915617086</v>
       </c>
       <c r="E47">
-        <v>-29.23789978284893</v>
+        <v>-30.28577281856483</v>
       </c>
       <c r="F47">
-        <v>1.605300497944279</v>
+        <v>1.852955843624442</v>
       </c>
       <c r="G47">
-        <v>-13.0797289600947</v>
+        <v>-12.66115665064258</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.123747332146697</v>
       </c>
       <c r="E48">
-        <v>-28.40204763593516</v>
+        <v>-29.17941001256586</v>
       </c>
       <c r="F48">
-        <v>1.607848556075291</v>
+        <v>2.808553852554729</v>
       </c>
       <c r="G48">
-        <v>-13.4484726389451</v>
+        <v>-12.95953453315068</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.348643610352814</v>
       </c>
       <c r="E49">
-        <v>-28.6382845394933</v>
+        <v>-28.90482146263676</v>
       </c>
       <c r="F49">
-        <v>1.995280960569036</v>
+        <v>2.709520872815243</v>
       </c>
       <c r="G49">
-        <v>-13.41155233395823</v>
+        <v>-12.67532496533626</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.553349598767265</v>
       </c>
       <c r="E50">
-        <v>-26.80190228837683</v>
+        <v>-28.48403565784404</v>
       </c>
       <c r="F50">
-        <v>1.695188301556859</v>
+        <v>2.160023356168191</v>
       </c>
       <c r="G50">
-        <v>-13.73046081976378</v>
+        <v>-14.85871377481118</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.749221049148275</v>
       </c>
       <c r="E51">
-        <v>-27.80159915336212</v>
+        <v>-28.49739918464067</v>
       </c>
       <c r="F51">
-        <v>2.174001227723029</v>
+        <v>2.793798972376064</v>
       </c>
       <c r="G51">
-        <v>-14.29266204053748</v>
+        <v>-12.81351689253383</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.940898282735938</v>
       </c>
       <c r="E52">
-        <v>-27.10412811517474</v>
+        <v>-26.59282264344269</v>
       </c>
       <c r="F52">
-        <v>2.318158693362616</v>
+        <v>2.302356756786813</v>
       </c>
       <c r="G52">
-        <v>-14.64155761017479</v>
+        <v>-13.61500775797315</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.133602996287483</v>
       </c>
       <c r="E53">
-        <v>-25.803070361927</v>
+        <v>-27.36049861417098</v>
       </c>
       <c r="F53">
-        <v>2.022933521209289</v>
+        <v>2.481688359084072</v>
       </c>
       <c r="G53">
-        <v>-14.24674134481305</v>
+        <v>-14.25819444866629</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.334825655939616</v>
       </c>
       <c r="E54">
-        <v>-25.49853954185918</v>
+        <v>-26.71650432554018</v>
       </c>
       <c r="F54">
-        <v>1.957987860095002</v>
+        <v>2.399098472290156</v>
       </c>
       <c r="G54">
-        <v>-14.7970366531583</v>
+        <v>-13.28697747623235</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.542968743589952</v>
       </c>
       <c r="E55">
-        <v>-25.07702465275122</v>
+        <v>-27.16940606799531</v>
       </c>
       <c r="F55">
-        <v>2.452993712251097</v>
+        <v>1.976579738083435</v>
       </c>
       <c r="G55">
-        <v>-14.69644260319962</v>
+        <v>-14.22214366739267</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.762804981642463</v>
       </c>
       <c r="E56">
-        <v>-24.26527304450627</v>
+        <v>-26.99066267043855</v>
       </c>
       <c r="F56">
-        <v>2.056204069575329</v>
+        <v>2.489678791051476</v>
       </c>
       <c r="G56">
-        <v>-14.69572237506732</v>
+        <v>-13.40390708772472</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.991859296236463</v>
       </c>
       <c r="E57">
-        <v>-24.30044570212385</v>
+        <v>-25.70337147817413</v>
       </c>
       <c r="F57">
-        <v>2.127210066608497</v>
+        <v>2.277557093481801</v>
       </c>
       <c r="G57">
-        <v>-15.21114978251114</v>
+        <v>-14.04017696337054</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.226696307506676</v>
       </c>
       <c r="E58">
-        <v>-22.91484586762691</v>
+        <v>-23.49977074130166</v>
       </c>
       <c r="F58">
-        <v>2.096789102108088</v>
+        <v>2.779844295108504</v>
       </c>
       <c r="G58">
-        <v>-15.83049019552101</v>
+        <v>-15.95525208287577</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.467605718055736</v>
       </c>
       <c r="E59">
-        <v>-23.81714884212923</v>
+        <v>-25.75747768561778</v>
       </c>
       <c r="F59">
-        <v>2.229483619627735</v>
+        <v>2.750074427386695</v>
       </c>
       <c r="G59">
-        <v>-14.77202882304299</v>
+        <v>-14.46238486631053</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.707109894608021</v>
       </c>
       <c r="E60">
-        <v>-23.12523424154926</v>
+        <v>-22.67131812091642</v>
       </c>
       <c r="F60">
-        <v>2.098256969145849</v>
+        <v>2.211416926572678</v>
       </c>
       <c r="G60">
-        <v>-15.21839636032517</v>
+        <v>-14.12584473645531</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.942521162770839</v>
       </c>
       <c r="E61">
-        <v>-21.44198233900216</v>
+        <v>-24.49439571539836</v>
       </c>
       <c r="F61">
-        <v>2.089116763223358</v>
+        <v>1.571721796904399</v>
       </c>
       <c r="G61">
-        <v>-16.08287683604116</v>
+        <v>-14.23075523337543</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.167251171107063</v>
       </c>
       <c r="E62">
-        <v>-22.47899382981066</v>
+        <v>-23.78945269509832</v>
       </c>
       <c r="F62">
-        <v>1.942399642309121</v>
+        <v>3.052816205353025</v>
       </c>
       <c r="G62">
-        <v>-15.37583921441201</v>
+        <v>-14.9044326754097</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.370104608642597</v>
       </c>
       <c r="E63">
-        <v>-21.74169939119982</v>
+        <v>-22.50581145288408</v>
       </c>
       <c r="F63">
-        <v>2.095975645318539</v>
+        <v>2.451149766412466</v>
       </c>
       <c r="G63">
-        <v>-15.63944271083312</v>
+        <v>-16.03862300086892</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.545100866810071</v>
       </c>
       <c r="E64">
-        <v>-21.29643265592163</v>
+        <v>-22.29790468271793</v>
       </c>
       <c r="F64">
-        <v>1.712219535358417</v>
+        <v>2.415679074224591</v>
       </c>
       <c r="G64">
-        <v>-16.35012084778247</v>
+        <v>-14.80171895632363</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.678729262479898</v>
       </c>
       <c r="E65">
-        <v>-21.68049706498616</v>
+        <v>-22.87504058109948</v>
       </c>
       <c r="F65">
-        <v>2.014065019794918</v>
+        <v>1.661699064196481</v>
       </c>
       <c r="G65">
-        <v>-15.15801860240983</v>
+        <v>-16.39225665443808</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.763788143287668</v>
       </c>
       <c r="E66">
-        <v>-21.47412997598261</v>
+        <v>-22.60671038224898</v>
       </c>
       <c r="F66">
-        <v>1.94820484106794</v>
+        <v>2.2965830359893</v>
       </c>
       <c r="G66">
-        <v>-15.84393500086083</v>
+        <v>-15.14946773902592</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.793105233998737</v>
       </c>
       <c r="E67">
-        <v>-20.59256288396141</v>
+        <v>-23.01976155343661</v>
       </c>
       <c r="F67">
-        <v>1.984369705139361</v>
+        <v>1.85673982592043</v>
       </c>
       <c r="G67">
-        <v>-15.43224505362964</v>
+        <v>-16.07513971560399</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.76075489541587</v>
       </c>
       <c r="E68">
-        <v>-20.83397583331032</v>
+        <v>-23.00302431350426</v>
       </c>
       <c r="F68">
-        <v>1.622537166861731</v>
+        <v>1.690652161659129</v>
       </c>
       <c r="G68">
-        <v>-16.39208603091699</v>
+        <v>-14.75063197725385</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.668801415623388</v>
       </c>
       <c r="E69">
-        <v>-20.51288891227046</v>
+        <v>-20.93943040752693</v>
       </c>
       <c r="F69">
-        <v>1.494749897836269</v>
+        <v>1.337714632552761</v>
       </c>
       <c r="G69">
-        <v>-15.18855365024202</v>
+        <v>-14.55054636778047</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.513719898372019</v>
       </c>
       <c r="E70">
-        <v>-21.37534131550528</v>
+        <v>-22.02778120816039</v>
       </c>
       <c r="F70">
-        <v>1.197356059822412</v>
+        <v>1.557061350609653</v>
       </c>
       <c r="G70">
-        <v>-15.24471503845348</v>
+        <v>-13.24996529704181</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.302219332407471</v>
       </c>
       <c r="E71">
-        <v>-20.10092004637066</v>
+        <v>-21.50699311185628</v>
       </c>
       <c r="F71">
-        <v>0.7863814537411049</v>
+        <v>1.304729042573284</v>
       </c>
       <c r="G71">
-        <v>-14.79385222763486</v>
+        <v>-15.221533208136</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.038184566911848</v>
       </c>
       <c r="E72">
-        <v>-20.59941899360902</v>
+        <v>-22.05768725050705</v>
       </c>
       <c r="F72">
-        <v>1.154194804666947</v>
+        <v>1.276423728419625</v>
       </c>
       <c r="G72">
-        <v>-15.00870005290418</v>
+        <v>-14.97596002418404</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.726979042299817</v>
       </c>
       <c r="E73">
-        <v>-20.44868420778971</v>
+        <v>-21.37627870962487</v>
       </c>
       <c r="F73">
-        <v>0.9128714994137839</v>
+        <v>0.4944333030332528</v>
       </c>
       <c r="G73">
-        <v>-15.04227679312198</v>
+        <v>-14.83090050026255</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.3794395694243</v>
       </c>
       <c r="E74">
-        <v>-20.73124287197231</v>
+        <v>-22.66964711400759</v>
       </c>
       <c r="F74">
-        <v>0.8875731589322869</v>
+        <v>0.8435851931088276</v>
       </c>
       <c r="G74">
-        <v>-14.94222086349905</v>
+        <v>-14.49883759722518</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.000333407478904</v>
       </c>
       <c r="E75">
-        <v>-20.10278124918781</v>
+        <v>-21.9456029903432</v>
       </c>
       <c r="F75">
-        <v>0.882697388399409</v>
+        <v>0.8346901839375664</v>
       </c>
       <c r="G75">
-        <v>-14.88566080686812</v>
+        <v>-14.98466838620281</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.603632278794911</v>
       </c>
       <c r="E76">
-        <v>-21.93221229270252</v>
+        <v>-22.24548306760514</v>
       </c>
       <c r="F76">
-        <v>0.8152599981375013</v>
+        <v>0.4582767226358599</v>
       </c>
       <c r="G76">
-        <v>-14.84108541198306</v>
+        <v>-13.65667270933498</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.200100405175331</v>
       </c>
       <c r="E77">
-        <v>-21.74287679444182</v>
+        <v>-22.20946811382213</v>
       </c>
       <c r="F77">
-        <v>0.3989772137390545</v>
+        <v>0.6555259118556727</v>
       </c>
       <c r="G77">
-        <v>-14.20831003729805</v>
+        <v>-13.22286568818236</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.798192014593836</v>
       </c>
       <c r="E78">
-        <v>-21.70463835992105</v>
+        <v>-22.03510375063079</v>
       </c>
       <c r="F78">
-        <v>0.484999855050172</v>
+        <v>0.2042222387690712</v>
       </c>
       <c r="G78">
-        <v>-13.53570391410294</v>
+        <v>-12.88675375774064</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.411620650282618</v>
       </c>
       <c r="E79">
-        <v>-22.46876400702733</v>
+        <v>-24.28609496799354</v>
       </c>
       <c r="F79">
-        <v>0.6768000434943695</v>
+        <v>0.5422731772797298</v>
       </c>
       <c r="G79">
-        <v>-13.10106018145265</v>
+        <v>-13.26331330634563</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.04411902748052</v>
       </c>
       <c r="E80">
-        <v>-22.92114950344558</v>
+        <v>-23.54097079782344</v>
       </c>
       <c r="F80">
-        <v>0.4945931779419931</v>
+        <v>0.2576685035976953</v>
       </c>
       <c r="G80">
-        <v>-12.84617817193655</v>
+        <v>-12.14864624916511</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.703173205860344</v>
       </c>
       <c r="E81">
-        <v>-22.65357103128036</v>
+        <v>-23.91440687839197</v>
       </c>
       <c r="F81">
-        <v>0.3581710071097481</v>
+        <v>1.14576865144567</v>
       </c>
       <c r="G81">
-        <v>-12.86965531219437</v>
+        <v>-11.40766439050351</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.39333442773571</v>
       </c>
       <c r="E82">
-        <v>-23.20420629976903</v>
+        <v>-24.26495152285172</v>
       </c>
       <c r="F82">
-        <v>-0.03069364462343784</v>
+        <v>0.109356775433069</v>
       </c>
       <c r="G82">
-        <v>-12.7374909890015</v>
+        <v>-11.21651682855805</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.111305305120845</v>
       </c>
       <c r="E83">
-        <v>-23.28666075450069</v>
+        <v>-24.2417340366144</v>
       </c>
       <c r="F83">
-        <v>-0.008544757007384652</v>
+        <v>0.1246393256473171</v>
       </c>
       <c r="G83">
-        <v>-12.56344843504543</v>
+        <v>-12.31495824512712</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.861097007566199</v>
       </c>
       <c r="E84">
-        <v>-24.45469911224712</v>
+        <v>-25.55867314820704</v>
       </c>
       <c r="F84">
-        <v>-0.007959929621008202</v>
+        <v>0.4663218268518488</v>
       </c>
       <c r="G84">
-        <v>-11.83632317502936</v>
+        <v>-10.6309139356224</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.638265902914638</v>
       </c>
       <c r="E85">
-        <v>-25.30549069491219</v>
+        <v>-24.9488371390161</v>
       </c>
       <c r="F85">
-        <v>-0.0336053560442781</v>
+        <v>-0.441620205395383</v>
       </c>
       <c r="G85">
-        <v>-11.26899012373669</v>
+        <v>-10.83965212634803</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.44074931072739</v>
       </c>
       <c r="E86">
-        <v>-26.40043948217483</v>
+        <v>-26.27461583187171</v>
       </c>
       <c r="F86">
-        <v>-0.4291930376185848</v>
+        <v>-0.07047930261249528</v>
       </c>
       <c r="G86">
-        <v>-11.43092497013841</v>
+        <v>-10.24894365266588</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.26916853739729</v>
       </c>
       <c r="E87">
-        <v>-26.98664591399375</v>
+        <v>-28.62690448431203</v>
       </c>
       <c r="F87">
-        <v>-0.5977947969473821</v>
+        <v>-0.7865540486559027</v>
       </c>
       <c r="G87">
-        <v>-10.77009679173092</v>
+        <v>-10.35403461677177</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.119964662354536</v>
       </c>
       <c r="E88">
-        <v>-28.4056704151413</v>
+        <v>-28.33590021610512</v>
       </c>
       <c r="F88">
-        <v>-0.7756220840411576</v>
+        <v>-1.351122881829489</v>
       </c>
       <c r="G88">
-        <v>-10.82102463155506</v>
+        <v>-10.87322558534427</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.997052244960883</v>
       </c>
       <c r="E89">
-        <v>-28.95319915046071</v>
+        <v>-30.51290975360455</v>
       </c>
       <c r="F89">
-        <v>-0.941670815034527</v>
+        <v>-0.5889958783948458</v>
       </c>
       <c r="G89">
-        <v>-10.55284054983697</v>
+        <v>-10.35801145730182</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.90381072342979</v>
       </c>
       <c r="E90">
-        <v>-30.32671701630518</v>
+        <v>-32.08834548274004</v>
       </c>
       <c r="F90">
-        <v>-1.314192606277881</v>
+        <v>-0.9489571347095513</v>
       </c>
       <c r="G90">
-        <v>-10.27683403592116</v>
+        <v>-10.39209678686133</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.842542765647291</v>
       </c>
       <c r="E91">
-        <v>-31.36543347757756</v>
+        <v>-32.92483388025189</v>
       </c>
       <c r="F91">
-        <v>-1.664542315617904</v>
+        <v>-1.393124422621035</v>
       </c>
       <c r="G91">
-        <v>-9.717900911820665</v>
+        <v>-9.961892546980975</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.819446463067236</v>
       </c>
       <c r="E92">
-        <v>-33.33482380301033</v>
+        <v>-35.54974798913899</v>
       </c>
       <c r="F92">
-        <v>-2.129408019823139</v>
+        <v>-1.836282759035909</v>
       </c>
       <c r="G92">
-        <v>-9.988234193660197</v>
+        <v>-8.974901101900004</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.838674406867718</v>
       </c>
       <c r="E93">
-        <v>-34.32598902296517</v>
+        <v>-35.131765309757</v>
       </c>
       <c r="F93">
-        <v>-2.389903888614097</v>
+        <v>-1.852139367860297</v>
       </c>
       <c r="G93">
-        <v>-10.04817226788657</v>
+        <v>-10.1035428817022</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.902772011690983</v>
       </c>
       <c r="E94">
-        <v>-36.51622849727801</v>
+        <v>-37.69643260044605</v>
       </c>
       <c r="F94">
-        <v>-2.621909717320571</v>
+        <v>-2.404820300436308</v>
       </c>
       <c r="G94">
-        <v>-10.79755405374036</v>
+        <v>-10.55847112603298</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.01610710956292</v>
       </c>
       <c r="E95">
-        <v>-38.13237747197946</v>
+        <v>-40.15179384977495</v>
       </c>
       <c r="F95">
-        <v>-2.907538253112466</v>
+        <v>-2.541566362923047</v>
       </c>
       <c r="G95">
-        <v>-10.18478592751405</v>
+        <v>-10.77000491752726</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.18036658267923</v>
       </c>
       <c r="E96">
-        <v>-40.36824132191958</v>
+        <v>-41.45946317507389</v>
       </c>
       <c r="F96">
-        <v>-2.895049786147861</v>
+        <v>-2.770847691241714</v>
       </c>
       <c r="G96">
-        <v>-10.7867489911451</v>
+        <v>-10.73838378535889</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.389925369611845</v>
       </c>
       <c r="E97">
-        <v>-41.84891193973355</v>
+        <v>-42.7675242133745</v>
       </c>
       <c r="F97">
-        <v>-3.491081670014578</v>
+        <v>-3.305355071367706</v>
       </c>
       <c r="G97">
-        <v>-10.98486258646126</v>
+        <v>-10.46758785127948</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.650494128129802</v>
       </c>
       <c r="E98">
-        <v>-43.47165210835315</v>
+        <v>-43.97069447247243</v>
       </c>
       <c r="F98">
-        <v>-3.942368775753123</v>
+        <v>-3.61945459479382</v>
       </c>
       <c r="G98">
-        <v>-11.08309907872947</v>
+        <v>-11.24345893878265</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.939725172633922</v>
       </c>
       <c r="E99">
-        <v>-45.90469930200926</v>
+        <v>-45.98213620754043</v>
       </c>
       <c r="F99">
-        <v>-4.102003457946616</v>
+        <v>-4.070739215430157</v>
       </c>
       <c r="G99">
-        <v>-11.16613367151278</v>
+        <v>-11.69537830294342</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.271086574090376</v>
       </c>
       <c r="E100">
-        <v>-47.83897357574955</v>
+        <v>-48.45137722970284</v>
       </c>
       <c r="F100">
-        <v>-4.67549877825277</v>
+        <v>-3.693749210416102</v>
       </c>
       <c r="G100">
-        <v>-11.23121670114437</v>
+        <v>-11.89131644836566</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.596238595071417</v>
       </c>
       <c r="E101">
-        <v>-49.23381036510364</v>
+        <v>-49.6694959815001</v>
       </c>
       <c r="F101">
-        <v>-4.576542836681743</v>
+        <v>-3.871461354440888</v>
       </c>
       <c r="G101">
-        <v>-11.33850280247353</v>
+        <v>-12.70351065853189</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.957507046647007</v>
       </c>
       <c r="E102">
-        <v>-50.98548864202514</v>
+        <v>-52.36499654686325</v>
       </c>
       <c r="F102">
-        <v>-4.72744983991934</v>
+        <v>-3.634618688469468</v>
       </c>
       <c r="G102">
-        <v>-12.44494055598297</v>
+        <v>-11.79701085952566</v>
       </c>
     </row>
   </sheetData>
